--- a/src/analysis/formant_results_all_vowels_model_standard.xlsx
+++ b/src/analysis/formant_results_all_vowels_model_standard.xlsx
@@ -436,12 +436,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>F1_mean</t>
+          <t>F1_mid_mean</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>F2_mean</t>
+          <t>F2_mid_mean</t>
         </is>
       </c>
     </row>
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>599.9752559370543</v>
+        <v>573.2508744340857</v>
       </c>
       <c r="D2" t="n">
-        <v>1111.359312100534</v>
+        <v>1018.915274825678</v>
       </c>
     </row>
     <row r="3">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>450.3737884607929</v>
+        <v>454.9736402533687</v>
       </c>
       <c r="D3" t="n">
-        <v>1918.021890302527</v>
+        <v>1935.437596342123</v>
       </c>
     </row>
     <row r="4">
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>342.8857600940456</v>
+        <v>340.850615615494</v>
       </c>
       <c r="D4" t="n">
-        <v>2104.07676233429</v>
+        <v>2098.134697239299</v>
       </c>
     </row>
     <row r="5">
@@ -503,10 +503,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>370.7573236909021</v>
+        <v>371.2263311600728</v>
       </c>
       <c r="D5" t="n">
-        <v>704.0977383689062</v>
+        <v>737.7337963020947</v>
       </c>
     </row>
     <row r="6">
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>361.5056946373037</v>
+        <v>354.798083133915</v>
       </c>
       <c r="D6" t="n">
-        <v>1086.596289888406</v>
+        <v>1005.757279782782</v>
       </c>
     </row>
   </sheetData>

--- a/src/analysis/formant_results_all_vowels_model_standard.xlsx
+++ b/src/analysis/formant_results_all_vowels_model_standard.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,16 @@
           <t>F2_mid_mean</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>F1_mid_mean(z)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>F2_mid_mean(z)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -460,6 +470,12 @@
       <c r="D2" t="n">
         <v>1018.915274825678</v>
       </c>
+      <c r="E2" t="n">
+        <v>1.369334284817008</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.535360508666695</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -476,6 +492,12 @@
       <c r="D3" t="n">
         <v>1935.437596342123</v>
       </c>
+      <c r="E3" t="n">
+        <v>0.319213958224415</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9065967074435456</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -492,6 +514,12 @@
       <c r="D4" t="n">
         <v>2098.134697239299</v>
       </c>
+      <c r="E4" t="n">
+        <v>-0.6940233628423768</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.16256675113079</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -508,6 +536,12 @@
       <c r="D5" t="n">
         <v>737.7337963020947</v>
       </c>
+      <c r="E5" t="n">
+        <v>-0.4243336245837088</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.9777410731932428</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -523,6 +557,12 @@
       </c>
       <c r="D6" t="n">
         <v>1005.757279782782</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.5701912556153401</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.5560618767143963</v>
       </c>
     </row>
   </sheetData>

--- a/src/analysis/formant_results_all_vowels_model_standard.xlsx
+++ b/src/analysis/formant_results_all_vowels_model_standard.xlsx
@@ -429,140 +429,145 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>vowel_label</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>vowel_label</t>
+          <t>F1_mid_mean</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>F1_mid_mean</t>
+          <t>F2_mid_mean</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>F2_mid_mean</t>
+          <t>F1_mid_mean(z)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>F1_mid_mean(z)</t>
+          <t>F2_mid_mean(z)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>F2_mid_mean(z)</t>
+          <t>duration</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>573.2508744340857</v>
+      </c>
       <c r="C2" t="n">
-        <v>573.2508744340857</v>
+        <v>1018.915274825678</v>
       </c>
       <c r="D2" t="n">
-        <v>1018.915274825678</v>
+        <v>1.369334284817008</v>
       </c>
       <c r="E2" t="n">
-        <v>1.369334284817008</v>
+        <v>-0.535360508666695</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.535360508666695</v>
+        <v>0.1020320429175069</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>ae</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>454.9736402533687</v>
+      </c>
       <c r="C3" t="n">
-        <v>454.9736402533687</v>
+        <v>1935.437596342123</v>
       </c>
       <c r="D3" t="n">
-        <v>1935.437596342123</v>
+        <v>0.319213958224415</v>
       </c>
       <c r="E3" t="n">
-        <v>0.319213958224415</v>
+        <v>0.9065967074435456</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9065967074435456</v>
+        <v>0.1284254977113663</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>i</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>340.850615615494</v>
+      </c>
       <c r="C4" t="n">
-        <v>340.850615615494</v>
+        <v>2098.134697239299</v>
       </c>
       <c r="D4" t="n">
-        <v>2098.134697239299</v>
+        <v>-0.6940233628423768</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6940233628423768</v>
+        <v>1.16256675113079</v>
       </c>
       <c r="F4" t="n">
-        <v>1.16256675113079</v>
+        <v>0.1154647399056731</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>o</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>371.2263311600728</v>
+      </c>
       <c r="C5" t="n">
-        <v>371.2263311600728</v>
+        <v>737.7337963020947</v>
       </c>
       <c r="D5" t="n">
-        <v>737.7337963020947</v>
+        <v>-0.4243336245837088</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4243336245837088</v>
+        <v>-0.9777410731932428</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9777410731932428</v>
+        <v>0.09870612224862865</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>354.798083133915</v>
+      </c>
       <c r="C6" t="n">
-        <v>354.798083133915</v>
+        <v>1005.757279782782</v>
       </c>
       <c r="D6" t="n">
-        <v>1005.757279782782</v>
+        <v>-0.5701912556153401</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5701912556153401</v>
+        <v>-0.5560618767143963</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5560618767143963</v>
+        <v>0.08385820083527974</v>
       </c>
     </row>
   </sheetData>
